--- a/public/exports-60-250/29189897.xlsx
+++ b/public/exports-60-250/29189897.xlsx
@@ -9041,40 +9041,40 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Bagvejen 1</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6064</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">5023161</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J121">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311818306</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2035-03-18</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,17 +9116,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændkjærgade 92</t>
+          <t xml:space="preserve">Bagvejen 3</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">6000</t>
+          <t xml:space="preserve">6064</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">7841251</t>
+          <t xml:space="preserve">5023161</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -9135,21 +9135,21 @@
         </is>
       </c>
       <c r="J122">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781557</t>
+          <t xml:space="preserve">311818305</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-30</t>
+          <t xml:space="preserve">2035-03-18</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,30 +9191,30 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagvejen 1</t>
+          <t xml:space="preserve">Hjarupvej 14</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">6064</t>
+          <t xml:space="preserve">6640</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5023161</t>
+          <t xml:space="preserve">5027423</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J123">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311818306</t>
+          <t xml:space="preserve">311818307</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9266,30 +9266,30 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagvejen 3</t>
+          <t xml:space="preserve">Herredsvej 45</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">6064</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5023161</t>
+          <t xml:space="preserve">9071031</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J124">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311818305</t>
+          <t xml:space="preserve">311826636</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-18</t>
+          <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,17 +9341,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjarupvej 14</t>
+          <t xml:space="preserve">Herredsvej 45</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">6640</t>
+          <t xml:space="preserve">6580</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5027423</t>
+          <t xml:space="preserve">9071031</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -9360,11 +9360,11 @@
         </is>
       </c>
       <c r="J125">
-        <v>96</v>
+        <v>218</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311818307</t>
+          <t xml:space="preserve">311826636</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-18</t>
+          <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9431,15 +9431,15 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J126">
-        <v>130</v>
+        <v>218</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826636</t>
+          <t xml:space="preserve">311826640</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9506,15 +9506,15 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J127">
-        <v>218</v>
+        <v>100</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826636</t>
+          <t xml:space="preserve">311826641</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9566,30 +9566,30 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herredsvej 45</t>
+          <t xml:space="preserve">Birkevej 9A</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6070</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9071031</t>
+          <t xml:space="preserve">5170804</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J128">
-        <v>218</v>
+        <v>93</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826640</t>
+          <t xml:space="preserve">311832714</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-23</t>
+          <t xml:space="preserve">2035-05-19</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9641,40 +9641,40 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herredsvej 45</t>
+          <t xml:space="preserve">Zahnsgade 12</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9071031</t>
+          <t xml:space="preserve">5676445</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J129">
-        <v>100</v>
+        <v>195</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826641</t>
+          <t xml:space="preserve">311868470</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-23</t>
+          <t xml:space="preserve">2035-11-16</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,40 +9716,40 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevej 9A</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">6070</t>
+          <t xml:space="preserve">6000</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5170804</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J130">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832714</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-19</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zahnsgade 12</t>
+          <t xml:space="preserve">Brændkjærgade 92</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9801,30 +9801,30 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5676445</t>
+          <t xml:space="preserve">7841251</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J131">
-        <v>195</v>
+        <v>92</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868470</t>
+          <t xml:space="preserve">311929645</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-16</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
